--- a/menu_actuel.xlsx
+++ b/menu_actuel.xlsx
@@ -7,31 +7,32 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Poulet Basquaise" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Blanquette de Veau" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Boeuf Bourguignon" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lasagnes Bolognaise" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Risotto aux Champignons" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Hachis Parmentier" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Curry de Pois Chiches" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Tartiflette" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Quiche Lorraine" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Chili con Carne" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Poulet Coco Curry" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Gratin Dauphinois" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Couscous Express" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Tacos au Poulet" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Ratatouille" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Pâtes Carbonara" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Saumon Teriyaki" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Moussaka" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Fajitas au Boeuf" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Wok Nouilles Crevettes" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Burger Maison" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Salade César" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Tajine Poulet Citron" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Paella Express" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Gnocchis Pesto Tomates" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Catégories" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Poulet Basquaise" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Blanquette de Veau" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Boeuf Bourguignon" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lasagnes Bolognaise" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Risotto aux Champignons" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Hachis Parmentier" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Curry de Pois Chiches" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Tartiflette" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Quiche Lorraine" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Chili con Carne" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Poulet Coco Curry" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Gratin Dauphinois" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Couscous Express" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Tacos au Poulet" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Ratatouille" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Pâtes Carbonara" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Saumon Teriyaki" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Moussaka" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Fajitas au Boeuf" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Wok Nouilles Crevettes" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Burger Maison" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Salade César" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Tajine Poulet Citron" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Paella Express" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Gnocchis Pesto Tomates" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -449,98 +450,318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Ingrédient</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Quantité</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Unité</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>Poulet Basquaise</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Plat</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Poivron rouge</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>Blanquette de Veau</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Plat</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomate</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>Boeuf Bourguignon</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Plat</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>Lasagnes Bolognaise</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Plat</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gousse d'ail</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>Risotto aux Champignons</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hachis Parmentier</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Curry de Pois Chiches</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tartiflette</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Quiche Lorraine</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Entrée</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chili con Carne</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Poulet Coco Curry</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gratin Dauphinois</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Couscous Express</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tacos au Poulet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ratatouille</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Entrée</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pâtes Carbonara</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Saumon Teriyaki</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Moussaka</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fajitas au Boeuf</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Wok Nouilles Crevettes</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Burger Maison</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Salade César</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Entrée</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tajine Poulet Citron</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Paella Express</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Plat</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gnocchis Pesto Tomates</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Plat</t>
         </is>
       </c>
     </row>
@@ -578,26 +799,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
+          <t>Pâte brisée</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Haricots rouges</t>
+          <t>Lardons</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -608,45 +829,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Épices Chili</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sachet(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -684,45 +905,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Viande hachée</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Haricots rouges</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poudre de curry</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -744,15 +965,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Épices Chili</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>sachet(s)</t>
         </is>
       </c>
     </row>
@@ -790,26 +1011,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pomme de terre</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,26 +1041,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crème liquide</t>
+          <t>Poudre de curry</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gousse d'ail</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -850,15 +1071,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Noix de muscade</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pincée(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -896,75 +1117,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Semoule</t>
+          <t>Pomme de terre</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Merguez</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Légumes à couscous</t>
+          <t>Crème liquide</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pois chiches</t>
+          <t>Gousse d'ail</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Épices Ras el Hanout</t>
+          <t>Noix de muscade</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pincée(s)</t>
         </is>
       </c>
     </row>
@@ -1002,75 +1223,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Galettes tortillas</t>
+          <t>Semoule</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Merguez</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Légumes à couscous</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oignon rouge</t>
+          <t>Pois chiches</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Épices mexicaines</t>
+          <t>Épices Ras el Hanout</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sachet(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
@@ -1108,11 +1329,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Courgette</t>
+          <t>Galettes tortillas</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1123,15 +1344,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aubergine</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1153,11 +1374,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Oignon rouge</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1168,7 +1389,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Épices mexicaines</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1176,7 +1397,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>sachet(s)</t>
         </is>
       </c>
     </row>
@@ -1214,41 +1435,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Spaghetti</t>
+          <t>Courgette</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>400</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Guanciale ou Lardons</t>
+          <t>Aubergine</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,22 +1480,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pecorino ou Parmesan</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Poivre noir</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1282,7 +1503,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pincée(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1320,56 +1541,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pavé de saumon</t>
+          <t>Spaghetti</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Guanciale ou Lardons</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Miel</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Pecorino ou Parmesan</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1380,7 +1601,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brocoli</t>
+          <t>Poivre noir</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1388,7 +1609,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>pincée(s)</t>
         </is>
       </c>
     </row>
@@ -1426,11 +1647,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aubergine</t>
+          <t>Pavé de saumon</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1441,60 +1662,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée (agneau ou boeuf)</t>
+          <t>Sauce soja</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sauce tomate</t>
+          <t>Miel</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait (béchamel)</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fromage râpé</t>
+          <t>Brocoli</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1532,11 +1753,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Galettes tortillas</t>
+          <t>Aubergine</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1547,11 +1768,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boeuf (bavette)</t>
+          <t>Viande hachée (agneau ou boeuf)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1562,45 +1783,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivron mix</t>
+          <t>Sauce tomate</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Lait (béchamel)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Épices Fajitas</t>
+          <t>Fromage râpé</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sachet(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1638,26 +1859,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Viande de veau</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>800</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Poivron rouge</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1668,45 +1889,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Champignon de Paris</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Gousse d'ail</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cube(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1744,22 +1965,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nouilles asiatiques</t>
+          <t>Galettes tortillas</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>250</v>
+        <v>8</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Crevettes décortiquées</t>
+          <t>Boeuf (bavette)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1774,11 +1995,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Poivron mix</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1789,22 +2010,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brocoli</t>
+          <t>Épices Fajitas</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1812,7 +2033,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>sachet(s)</t>
         </is>
       </c>
     </row>
@@ -1850,41 +2071,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pain burger</t>
+          <t>Nouilles asiatiques</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Steak haché</t>
+          <t>Crevettes décortiquées</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cheddar en tranches</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1895,26 +2116,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Salade</t>
+          <t>Sauce soja</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Brocoli</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1956,11 +2177,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Salade Romaine</t>
+          <t>Pain burger</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1971,11 +2192,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Steak haché</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1986,45 +2207,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Croûtons</t>
+          <t>Cheddar en tranches</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Salade</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sauce César</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pot</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -2062,11 +2283,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cuisse de poulet</t>
+          <t>Salade Romaine</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2077,7 +2298,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Citron confit</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2092,7 +2313,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Olives vertes</t>
+          <t>Croûtons</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2107,22 +2328,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Épices Tajine</t>
+          <t>Sauce César</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2130,7 +2351,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pot</t>
         </is>
       </c>
     </row>
@@ -2168,37 +2389,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Riz à paella</t>
+          <t>Cuisse de poulet</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>300</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Crevettes</t>
+          <t>Citron confit</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Olives vertes</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2213,22 +2434,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Petit pois</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Safran ou Spigol</t>
+          <t>Épices Tajine</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2236,7 +2457,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dose</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
@@ -2274,6 +2495,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Riz à paella</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Crevettes</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>200</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Petit pois</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Safran ou Spigol</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Gnocchis</t>
         </is>
       </c>
@@ -2380,7 +2707,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Viande de boeuf</t>
+          <t>Viande de veau</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2395,60 +2722,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lardons</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vin rouge</t>
+          <t>Champignon de Paris</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cube(s)</t>
         </is>
       </c>
     </row>
@@ -2486,11 +2813,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
+          <t>Viande de boeuf</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2501,60 +2828,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Feuilles de lasagne</t>
+          <t>Lardons</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sauce tomate</t>
+          <t>Vin rouge</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gruyère râpé</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -2592,11 +2919,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Riz Arborio</t>
+          <t>Viande hachée</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2607,26 +2934,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Champignons</t>
+          <t>Feuilles de lasagne</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300</v>
+        <v>12</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Sauce tomate</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2637,30 +2964,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Gruyère râpé</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -2698,11 +3025,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
+          <t>Riz Arborio</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2713,11 +3040,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pomme de terre</t>
+          <t>Champignons</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2728,30 +3055,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -2804,11 +3131,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pois chiches (conserve)</t>
+          <t>Viande hachée</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2819,60 +3146,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Pomme de terre</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pâte de curry</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -2910,41 +3237,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pomme de terre</t>
+          <t>Pois chiches (conserve)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reblochon</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lardons</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2955,7 +3282,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Pâte de curry</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2963,22 +3290,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3343,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pâte brisée</t>
+          <t>Pomme de terre</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -3024,63 +3351,63 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lardons</t>
+          <t>Reblochon</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Lardons</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/menu_actuel.xlsx
+++ b/menu_actuel.xlsx
@@ -7,36 +7,41 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Risotto aux Crevettes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Quiche Au Thon" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Poulet Basquaise" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Blanquette de Veau" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Boeuf Bourguignon" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Lasagnes Bolognaise" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Risotto aux Champignons" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Hachis Parmentier" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Curry de Pois Chiches" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tartiflette" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Quiche Lorraine" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Chili con Carne" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Poulet Coco Curry" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Gratin Dauphinois" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Couscous Express" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Tacos au Poulet" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Ratatouille" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Pâtes Carbonara" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Saumon Teriyaki" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Moussaka" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Fajitas au Boeuf" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Wok Nouilles Crevettes" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Burger Maison" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Salade César" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Tajine Poulet Citron" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Paella Express" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Gnocchis Pesto Tomates" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Mousse au Chocolat" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Banofee" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Mi-Cuit Chocolat" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Taboulé" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dhal de lentilles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Lentilles vertes au thym" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Salade de mangue à la thaï" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ratatouille" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Salade de pâtes tomates et feta" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Couscous aux légumes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Risotto forestier" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gratin pâtes tomates confites pesto" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Galettes de carottes au cumin" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Chili sin carne" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Rougail saucisses" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Poulet au curry rouge" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Poulet basquaise" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Lentilles aux saucisses" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Lasagnes au boeuf" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Lapin à la moutarde" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Quiche lorraine" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Filet mignon sauce forestière" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Chili con carne" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Nouilles chinoises au boeuf" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Encornet au curry vert" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Risotto de quinoa aux crevettes" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Crumble poireaux saumon" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Crevettes au lait de coco" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Parmentier de poissons" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Saumon sauce soja" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Fondant au chocolat noir" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Mousse au chocolat" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Tiramisu" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Banana bread" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Cheesecake" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Invisible aux pommes" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Riz au lait" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Semoule aux raisins" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -478,11 +483,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz Arborio</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>300</v>
+          <t>Semoule</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -493,37 +500,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crevettes</t>
+          <t>Tomates</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Concombre</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Persil</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -531,37 +538,54 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
+          <t>Menthe</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Petits pois</t>
+          <t>Oignons blancs ou rouges</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Citron</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -587,7 +611,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -612,52 +636,58 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pomme de terre</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
+          <t>Carotte</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reblochon</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
+          <t>Cumin</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lardons</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>200</v>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -665,22 +695,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>15</v>
+          <t>Coriandre</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>bouquet(s)</t>
         </is>
       </c>
     </row>
@@ -706,7 +738,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -731,26 +763,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pâte brisée</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
+          <t>Haricots rouges</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lardons</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>200</v>
+          <t>Tomates concassées</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -761,11 +797,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
+          <t>Poivron</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -776,30 +814,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>20</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>20</v>
+          <t>Épices Chili</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>sachet(s)</t>
         </is>
       </c>
     </row>
@@ -814,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -850,11 +892,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>500</v>
+          <t>Saucisses fumées</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -865,11 +909,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Haricots rouges</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>400</v>
+          <t>Tomates concassées</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -880,45 +926,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>400</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
+          <t>Ail</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>gousse(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Chili</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
+          <t>Curcuma</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sachet(s)</t>
+          <t>c.à.s</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Thym</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>c.à.s</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Riz Basmati</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>250</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -933,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,12 +1054,14 @@
           <t>Filet de poulet</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>4</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -987,8 +1071,10 @@
           <t>Lait de coco</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>40</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,11 +1085,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poudre de curry</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
+          <t>Pâte de curry rouge</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,8 +1105,10 @@
           <t>Oignon</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,15 +1119,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>250</v>
+          <t>Riz basmati</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Poivron</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,7 +1170,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1088,15 +1195,100 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>patate</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+          <t>Filet de poulet</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce</t>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Poivron rouge</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gousse d'ail</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Riz</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>250</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,11 +1339,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Semoule</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>300</v>
+          <t>Lentilles vertes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1162,11 +1356,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Merguez</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>8</v>
+          <t>Saucisses</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1177,43 +1373,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Légumes à couscous</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>600</v>
+          <t>Carotte</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pois chiches</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>200</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Ras el Hanout</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+          <t>Bouillon de volaille</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cube(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Thym</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>2</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>c.à.s</t>
         </is>
@@ -1230,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,75 +1483,128 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Galettes tortillas</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>8</v>
+          <t>Viande hachée</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>400</v>
+          <t>Feuilles de lasagne</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivron</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
+          <t>Sauce tomate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon rouge</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices mexicaines</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+          <t>Gruyère râpé</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>sachet(s)</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1360,7 +1630,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1385,11 +1655,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Courgette</t>
+          <t>Cuisse de Lapin</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1400,41 +1670,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aubergine</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>Moutarde</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tomate</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1445,13 +1719,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Tagliatelles</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -1468,7 +1757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,26 +1793,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spaghetti</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>400</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Guanciale ou Lardons</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>200</v>
+          <t>Lardons</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1537,8 +1830,10 @@
           <t>Oeuf</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1549,30 +1844,64 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pecorino ou Parmesan</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>100</v>
+          <t>Crème fraîche</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Poivre noir</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pincée(s)</t>
+          <t>cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>c.à.s</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fromage rapé</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,7 +1927,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1623,75 +1952,100 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pavé de saumon</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
+          <t>Filet mignon de porc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>10</v>
+          <t>Champignons</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Miel</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
+          <t>Crème fraîche</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>250</v>
+          <t>Échalote</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brocoli</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Grenailles</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1717,7 +2071,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1742,86 +2096,96 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pâte brisée</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
+          <t>Lentilles corail</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thon</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>200</v>
+          <t>Lait de coco</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
+          <t>Tomates concassées</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>20</v>
+          <t>Curry</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>20</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fromage rapé</t>
+          <t>Riz Basmati</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1840,7 +2204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1876,26 +2240,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aubergine</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
+          <t>Viande hachée de bœuf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Viande hachée (agneau ou boeuf)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>500</v>
+          <t>Haricots rouges</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1906,11 +2274,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sauce tomate</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>400</v>
+          <t>Tomates concassées</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1921,28 +2291,62 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lait (béchamel)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>50</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fromage râpé</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>100</v>
+          <t>Épices Chili</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>sachet(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Poivron</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Riz </t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>250</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -1959,7 +2363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1995,26 +2399,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Galettes tortillas</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>8</v>
+          <t>Nouilles asiatiques</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boeuf (bavette)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>400</v>
+          <t>Boeuf (rumsteack ou bavette)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2025,26 +2433,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivron mix</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
+          <t>Sauce soja</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
+          <t>Poivron</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2055,15 +2467,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Fajitas</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+          <t>Brocoli</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>sachet(s)</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Coriandre</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bouquet</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2114,11 +2558,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nouilles asiatiques</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>250</v>
+          <t>Encornets</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2129,58 +2575,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crevettes décortiquées</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>400</v>
+          <t>Lait de coco</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carotte</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
+          <t>Pâte de curry vert</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brocoli</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
+          <t>Riz basmati</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Poivrons</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -2197,7 +2666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2208,7 +2677,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2233,56 +2702,64 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pain burger</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
+          <t>Quinoa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Steak haché</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
+          <t>Crevettes</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cheddar en tranches</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
+          <t>Bouillon de légumes</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Salade</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2293,13 +2770,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tomate</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+          <t>Parmesan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Courgettes</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>2</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -2327,7 +2821,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2352,26 +2846,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Salade Romaine</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
+          <t>Pavé de saumon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>Poireaux</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2382,11 +2880,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Croûtons</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>100</v>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2397,11 +2897,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Parmesan</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>50</v>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2412,15 +2914,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sauce César</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
+          <t>Crème fraîche</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pot</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2446,7 +2950,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2471,75 +2975,100 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cuisse de poulet</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
+          <t>Crevettes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Citron confit</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>Lait de coco</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Olives vertes</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>100</v>
+          <t>Citron vert</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
+          <t>Ail</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>gousse(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Tajine</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
+          <t>Riz basmati</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -2554,7 +3083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2590,11 +3119,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz à paella</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>300</v>
+          <t>Filets de poisson blanc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2605,11 +3136,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crevettes</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>200</v>
+          <t>Pomme de terre</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2620,26 +3153,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chorizo</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>100</v>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Petit pois</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>100</v>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2650,15 +3187,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Safran ou Spigol</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+          <t>Chapelure</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Persil</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>dose</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>botte</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ail</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gousse(s)</t>
         </is>
       </c>
     </row>
@@ -2684,7 +3253,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2709,56 +3278,64 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gnocchis</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>600</v>
+          <t>Pavé de saumon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pesto vert</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>150</v>
+          <t>Sauce soja</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates cerises</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>250</v>
+          <t>Miel</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Parmesan</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>50</v>
+          <t>Riz basmati</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2769,15 +3346,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pignons de pin</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>30</v>
+          <t>Brocoli</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -2831,8 +3410,10 @@
           <t>Chocolat noir</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>200</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2843,56 +3424,64 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oeuf</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sucre</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>50</v>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème liquide</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>20</v>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beurre</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>30</v>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2911,7 +3500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2947,60 +3536,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Banane</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
+          <t>Chocolat noir</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Caramel au beurre salé</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>200</v>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème liquide entière</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>30</v>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biscuits digestifs</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>150</v>
+          <t>Crème liquide</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -3010,25 +3607,12 @@
           <t>Beurre</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>60</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sucre glace</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C8" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -3056,7 +3640,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3081,41 +3665,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
+          <t>Lentilles vertes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivron rouge</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
+          <t>Thym</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>càs</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomate</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
+          <t>Carotte</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3129,8 +3719,10 @@
           <t>Oignon</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>2</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3141,15 +3733,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gousse d'ail</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
+          <t>Bouillon de légumes</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cube(s)</t>
         </is>
       </c>
     </row>
@@ -3200,11 +3794,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chocolat noir</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>150</v>
+          <t>Biscuits à la cuillère</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3215,11 +3811,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Beurre</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>100</v>
+          <t>Mascarpone</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3233,8 +3831,10 @@
           <t>Oeuf</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3245,28 +3845,688 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sucre</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>80</v>
+          <t>Café fort</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Banane mûre</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Farine</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>250</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>85</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Oeufs</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Levure</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càc</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Biscuits speculoos</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>250</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fromage blanc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Crème fraîche</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>125</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Oeufs</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Citron vert</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Pomme</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>130</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Riz rond</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sucre vanillé</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sachet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>càs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Semoule fine</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Raisins secs</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -3283,7 +4543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3294,7 +4554,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3319,26 +4579,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande de veau</t>
+          <t>Mangue verte (dure)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>800</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Carottes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3349,45 +4609,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Champignon de Paris</t>
+          <t>Coriandre</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Gingembre</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>racine</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Cacahuètes</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sauce soja</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Citron vert</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>cube(s)</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -3402,7 +4692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3413,7 +4703,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3438,56 +4728,64 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande de boeuf</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>800</v>
+          <t>Courgette</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lardons</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>150</v>
+          <t>Aubergine</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vin rouge</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>50</v>
+          <t>Poivron</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Carotte</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3501,12 +4799,29 @@
           <t>Oignon</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>2</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Herbes de Provence</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càs</t>
         </is>
       </c>
     </row>
@@ -3521,7 +4836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3532,7 +4847,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3557,11 +4872,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
+          <t>Pâtes fusili ou penne</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3572,11 +4887,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Feuilles de lasagne</t>
+          <t>Tomates</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3587,11 +4902,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sauce tomate</t>
+          <t>Feta</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3602,28 +4917,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>50</v>
+          <t>Concombre</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gruyère râpé</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+          <t>Basilic</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>botte</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Olives noires</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>100</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -3640,7 +4974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3676,11 +5010,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz Arborio</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>300</v>
+          <t>Semoule</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3691,26 +5027,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Champignons</t>
+          <t>Poivrons</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Parmesan</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>80</v>
+          <t>Pois chiches</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3721,28 +5059,77 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
+          <t>Épices Ras el Hanout</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Bouillon de légumes</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cube(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Courgettes</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Oignon</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -3770,7 +5157,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3795,11 +5182,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>500</v>
+          <t>Riz Arborio</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3810,11 +5199,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pomme de terre</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>800</v>
+          <t>Champignons</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3825,30 +5216,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>20</v>
+          <t>Parmesan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beurre</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>50</v>
+          <t>Bouillon de légumes</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -3858,8 +5253,10 @@
           <t>Oignon</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3914,11 +5311,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pois chiches (conserve)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>400</v>
+          <t>Pâtes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3929,26 +5328,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>40</v>
+          <t>Tomates cerises confites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>400</v>
+          <t>Pesto vert</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3959,30 +5362,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pâte de curry</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
+          <t>Fromage râpé</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>250</v>
+          <t>Crème fraîche</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>

--- a/menu_actuel.xlsx
+++ b/menu_actuel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lconord.LYD\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19F2BEE1-6AD5-4B2C-98F3-CB8E8C1D841B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A4C4FD-360E-4012-9420-7A22E0C90DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Taboulé" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,6 @@
     <sheet name="Semoule aux raisins" sheetId="35" r:id="rId35"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -864,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -3597,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">

--- a/menu_actuel.xlsx
+++ b/menu_actuel.xlsx
@@ -11,43 +11,42 @@
     <sheet name="Poke bowl au saumon" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Taboulé" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Dhal de lentilles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Gaspacho de tomates" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Lentilles vertes au thym" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Salade de mangue à la thaï" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Ratatouille" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Salade de pâtes tomates et feta" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Couscous aux légumes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Risotto forestier" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Gratin pâtes tomates &amp; pesto" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Galettes de carottes au cumin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Chili sin carne" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Riz safrané au chorizo et crevettes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Rougail saucisses" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Poulet au curry rouge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Poulet basquaise" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Lentilles aux saucisses" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Lasagnes au boeuf" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Lapin à la moutarde" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Quiche lorraine" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Filet mignon sauce forestière" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Chili con carne" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Nouilles chinoises au boeuf" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Encornet au curry vert" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Risotto de quinoa aux crevettes" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Crumble poireaux saumon" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Crevettes au lait de coco" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Parmentier de poissons" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Cabillaud sauce vierge" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="Saumon sauce soja" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Fondant au chocolat noir" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="Mousse au chocolat" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="Tiramisu" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="Banana bread" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="Cheesecake" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="Croustade aux pommes" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="Riz au lait" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="Cookie au chocolat" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="Semoule aux raisins" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="Lentilles vertes au thym" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Salade de mangue à la thaï" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ratatouille" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Salade de pâtes tomates et feta" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Couscous aux légumes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Risotto forestier" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Gratin pâtes tomates &amp; pesto" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Galettes de carottes au cumin" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Chili sin carne" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Riz safrané au chorizo et crevettes" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Rougail saucisses" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Poulet au curry rouge" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Poulet basquaise" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Lentilles aux saucisses" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Lasagnes au boeuf" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Lapin à la moutarde" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Quiche lorraine" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Filet mignon sauce forestière" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Chili con carne" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Nouilles chinoises au boeuf" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Encornet au curry vert" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Risotto de quinoa aux crevettes" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Crumble poireaux saumon" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Crevettes au lait de coco" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Parmentier de poissons" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Cabillaud sauce vierge" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Saumon sauce soja" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Fondant au chocolat noir" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Mousse au chocolat" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Tiramisu" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Banana bread" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Cheesecake" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Croustade aux pommes" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Riz au lait" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Cookie au chocolat" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Semoule aux raisins" sheetId="40" state="visible" r:id="rId40"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -653,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,7 +688,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Semoule</t>
+          <t>Riz Arborio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -706,27 +705,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivrons</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>Champignons</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pois chiches</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -738,24 +739,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Épices Ras el Hanout</t>
+          <t>Bouillon de légumes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bouillon de légumes</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -764,51 +765,6 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>cube(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Courgettes</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Carottes</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -861,12 +817,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz Arborio</t>
+          <t>Pâtes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -878,12 +834,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Champignons</t>
+          <t>Tomates cerises confites</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -895,12 +851,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Pesto vert</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -912,34 +868,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bouillon de légumes</t>
+          <t>Fromage râpé</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -990,12 +946,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pâtes</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1007,68 +963,66 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates cerises confites</t>
+          <t>Cumin</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pesto vert</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fromage râpé</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Coriandre</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>bouquet(s)</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1073,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Haricots rouges</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1136,24 +1090,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cumin</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1170,22 +1124,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coriandre</t>
+          <t>Épices Chili</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1195,7 +1151,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bouquet(s)</t>
+          <t>sachet(s)</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1221,7 +1177,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1246,13 +1202,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Haricots rouges</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+          <t>Riz à paella</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1263,34 +1217,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+          <t>Poivron rouge</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivron</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Petit pois (surgelés)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1252,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1314,17 +1264,77 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Chili</t>
+          <t>Gousse d'ail</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sachet(s)</t>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bouillon de volaille</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cube(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Safran ou Spigol</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>càc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>tranche(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Crevettes</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1360,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1375,11 +1385,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz à paella</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>400</v>
+          <t>Saucisses fumées</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1390,71 +1402,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivron rouge</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
+          <t>Tomates concassées</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Petit pois (surgelés)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>150</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Ail</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>gousse(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gousse d'ail</t>
+          <t>Curcuma</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Thym</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1462,52 +1478,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cube(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Safran ou Spigol</t>
+          <t>Riz Basmati</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>càc</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Chorizo</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>16</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>tranche(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Crevettes</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1558,7 +1544,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Saucisses fumées</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1575,24 +1561,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Pâte de curry rouge</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1602,48 +1588,48 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ail</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gousse(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Curcuma</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Thym</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1651,22 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>c.à.s</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Riz Basmati</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>250</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1722,46 +1693,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Poivron rouge</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pâte de curry rouge</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1744,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1785,32 +1756,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Gousse d'ail</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1861,29 +1832,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Lentilles vertes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivron rouge</t>
+          <t>Saucisses</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1895,12 +1866,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1917,7 +1888,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1929,32 +1900,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gousse d'ail</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cube(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Thym</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2005,12 +1976,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lentilles vertes</t>
+          <t>Viande hachée</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2022,12 +1993,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Saucisses</t>
+          <t>Feuilles de lasagne</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2039,66 +2010,94 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Sauce tomate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>60</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Gruyère râpé</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cube(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Thym</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,79 +2327,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+          <t>Cuisse de Lapin</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Feuilles de lasagne</t>
+          <t>Moutarde</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sauce tomate</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+          <t>Crème fraîche</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>25</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>60</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gruyère râpé</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+          <t>Tagliatelles</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2411,43 +2406,13 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Carottes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>50</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -2464,7 +2429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2500,11 +2465,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cuisse de Lapin</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2515,79 +2482,98 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Moutarde</t>
+          <t>Lardons</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>25</v>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tagliatelles</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>600</v>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carottes</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fromage rapé</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2638,29 +2624,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Filet mignon de porc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lardons</t>
+          <t>Champignons</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2672,79 +2658,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Échalote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Grenailles</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>c.à.s</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fromage rapé</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>100</v>
-      </c>
-      <c r="C9" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -2761,7 +2732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2797,12 +2768,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet mignon de porc</t>
+          <t>Viande hachée de bœuf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2814,12 +2785,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Champignons</t>
+          <t>Haricots rouges</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2831,29 +2802,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Échalote</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2865,30 +2836,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Épices Chili</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>sachet(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Grenailles</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Riz </t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>250</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -2941,12 +2927,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée de bœuf</t>
+          <t>Nouilles asiatiques</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2958,7 +2944,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Haricots rouges</t>
+          <t>Boeuf (rumsteack ou bavette)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2975,29 +2961,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Sauce soja</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3009,7 +2995,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Chili</t>
+          <t>Brocoli</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3019,18 +3005,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sachet(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3041,15 +3027,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riz </t>
+          <t>Coriandre</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>bouquet</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3075,7 +3061,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3100,12 +3086,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nouilles asiatiques</t>
+          <t>Encornets</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3117,46 +3103,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boeuf (rumsteack ou bavette)</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Pâte de curry vert</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3168,47 +3154,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brocoli</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Poivrons</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Coriandre</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>bouquet</t>
         </is>
       </c>
     </row>
@@ -3259,12 +3230,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Encornets</t>
+          <t>Quinoa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3276,34 +3247,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Crevettes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pâte de curry vert</t>
+          <t>Bouillon de légumes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -3327,12 +3298,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3344,7 +3315,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Poivrons</t>
+          <t>Courgettes</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -3367,7 +3338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3403,12 +3374,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Quinoa</t>
+          <t>Pavé de saumon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3420,83 +3391,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crevettes</t>
+          <t>Poireaux</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bouillon de légumes</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Courgettes</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3547,12 +3503,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pavé de saumon</t>
+          <t>Crevettes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3564,68 +3520,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poireaux</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Citron vert</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Ail</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>gousse(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3676,7 +3647,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Crevettes</t>
+          <t>Filets de poisson blanc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3693,63 +3664,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Pomme de terre</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>800</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Citron vert</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ail</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gousse(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Chapelure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3761,15 +3732,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carottes</t>
+          <t>Persil</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>botte</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ail</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gousse(s)</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3973,13 +3959,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filets de poisson blanc</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+          <t>Cabillaud</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3990,68 +3974,64 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pomme de terre</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+          <t>Tomates</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Echalotes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Citron</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chapelure</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>Ciboulette</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>bouquet</t>
         </is>
       </c>
     </row>
@@ -4073,15 +4053,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ail</t>
+          <t>Gingembre</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gousse(s)</t>
+          <t>racine</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Patates douces</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>700</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Crème fraîche</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4132,37 +4142,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cabillaud</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>800</v>
+          <t>Pavé de saumon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>Sauce soja</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Echalotes</t>
+          <t>Miel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4172,99 +4186,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Citron</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ciboulette</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
+          <t>Brocoli</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bouquet</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Persil</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>botte</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Gingembre</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>racine</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Patates douces</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>700</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Crème fraîche</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4246,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Dessert</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -4315,63 +4271,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pavé de saumon</t>
+          <t>Chocolat noir</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Miel</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4383,17 +4339,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brocoli</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -4461,58 +4417,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Crème liquide</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4573,7 +4529,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chocolat noir</t>
+          <t>Biscuits à la cuillère</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4590,41 +4546,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Mascarpone</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème liquide</t>
+          <t>Café fort</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4641,12 +4597,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4666,7 +4622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4702,30 +4658,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Biscuits à la cuillère</t>
+          <t>Banane mûre</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mascarpone</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4736,34 +4690,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>85</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Café fort</t>
+          <t>Oeufs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -4773,14 +4725,27 @@
           <t>Sucre</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="B7" t="n">
+        <v>160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Levure</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càc</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4831,28 +4796,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Banane mûre</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Biscuits speculoos</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>250</v>
+          <t>Fromage blanc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4863,43 +4828,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oeufs</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -4910,7 +4875,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Levure</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4918,7 +4883,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>càc</t>
+          <t>càs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Oeufs</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Citron vert</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4969,47 +4964,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Biscuits speculoos</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>250</v>
+          <t>Pomme</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fromage blanc</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+          <t>Pâte Filo</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>feuille(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -5019,10 +5014,8 @@
           <t>Sucre</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="B6" t="n">
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5033,60 +5026,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Armagnac ou Calvados</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>càs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Oeufs</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Citron vert</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>ml</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5137,47 +5085,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pomme</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Riz rond</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pâte Filo</t>
+          <t>Sucre vanillé</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feuille(s)</t>
+          <t>sachet</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beurre</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>50</v>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -5188,26 +5136,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Armagnac ou Calvados</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>50</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ml</t>
+          <t>càs</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5258,7 +5191,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz rond</t>
+          <t>Chocolat</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5273,32 +5206,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sucre vanillé</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sachet</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -5309,11 +5240,41 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>càs</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Levure</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càc</t>
         </is>
       </c>
     </row>
@@ -5472,140 +5433,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Catégorie :</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Dessert</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ingrédient</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Quantité</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Unité</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Chocolat</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Beurre</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>85</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>150</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sucre</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>85</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Oeuf</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Levure</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>càc</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -5712,7 +5539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5723,7 +5550,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -5748,41 +5575,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tomates</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>6</v>
+          <t>Lentilles vertes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivrons rouges</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
+          <t>Thym</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>càs</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concombre</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
+          <t>Carotte</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5793,22 +5626,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Basilic</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Menthe</t>
+          <t>Bouillon de légumes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5818,82 +5653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>botte</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Oignons rouges</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Citron</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Poivrons verts</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tabasco </t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>goutte(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Croûtons</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>sachet</t>
+          <t>cube(s)</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5919,7 +5679,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -5944,85 +5704,105 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lentilles vertes</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
+          <t>Mangue verte (dure)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thym</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>càs</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carotte</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Coriandre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Gingembre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>racine</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bouillon de légumes</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Cacahuètes</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cube(s)</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sauce soja</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Citron vert</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -6037,7 +5817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6048,7 +5828,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -6073,11 +5853,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mangue verte (dure)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+          <t>Courgette</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -6088,11 +5870,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carottes</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>Aubergine</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -6103,75 +5887,66 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coriandre</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
+          <t>Poivron</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gingembre</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>racine</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cacahuètes</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>50</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Herbes de Provence</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>càs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Citron vert</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -6197,7 +5972,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -6222,30 +5997,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Courgette</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Pâtes fusili ou penne</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aubergine</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Tomates</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -6256,29 +6027,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivron</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Feta</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Concombre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6290,7 +6059,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Basilic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6300,22 +6069,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Herbes de Provence</t>
+          <t>Olives noires</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>càs</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6341,7 +6110,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -6366,11 +6135,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pâtes fusili ou penne</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>400</v>
+          <t>Semoule</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -6381,7 +6152,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates</t>
+          <t>Poivrons</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6396,11 +6167,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Feta</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>80</v>
+          <t>Pois chiches</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -6411,24 +6184,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Concombre</t>
+          <t>Épices Ras el Hanout</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Basilic</t>
+          <t>Bouillon de légumes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6438,22 +6211,52 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>cube(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Olives noires</t>
+          <t>Courgettes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>

--- a/menu_actuel.xlsx
+++ b/menu_actuel.xlsx
@@ -7,46 +7,45 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Boulettes de boeuf à la tomate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Poke bowl au saumon" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Taboulé" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dhal de lentilles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Lentilles vertes au thym" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Salade de mangue à la thaï" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Ratatouille" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Salade de pâtes tomates et feta" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Couscous aux légumes" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Risotto forestier" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Gratin pâtes tomates &amp; pesto" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Galettes de carottes au cumin" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Chili sin carne" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Riz safrané au chorizo et crevettes" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Rougail saucisses" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Poulet au curry rouge" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Poulet basquaise" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Lentilles aux saucisses" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Lasagnes au boeuf" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Lapin à la moutarde" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Quiche lorraine" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Filet mignon sauce forestière" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Chili con carne" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Nouilles chinoises au boeuf" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Encornet au curry vert" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Risotto de quinoa aux crevettes" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Crumble poireaux saumon" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Crevettes au lait de coco" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Parmentier de poissons" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Cabillaud sauce vierge" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Saumon sauce soja" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="Fondant au chocolat noir" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Mousse au chocolat" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="Tiramisu" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="Banana bread" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="Cheesecake" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="Croustade aux pommes" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="Riz au lait" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="Cookie au chocolat" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="Semoule aux raisins" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Poke bowl au saumon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Taboulé" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dhal de lentilles" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lentilles vertes au thym" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Salade de mangue à la thaï" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ratatouille" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Salade de pâtes tomates et feta" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Couscous aux légumes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Risotto forestier" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Gratin pâtes tomates &amp; pesto" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Galettes de carottes au cumin" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Chili sin carne" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Riz safrané au chorizo et crevettes" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Rougail saucisses" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Poulet au curry rouge" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Poulet basquaise" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Lentilles aux saucisses" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Lasagnes au boeuf" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Lapin à la moutarde" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Quiche lorraine" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Filet mignon sauce forestière" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Chili con carne" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Nouilles chinoises au boeuf" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Encornet au curry vert" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Risotto de quinoa aux crevettes" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Crumble poireaux saumon" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Crevettes au lait de coco" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Parmentier de poissons" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Cabillaud sauce vierge" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Saumon sauce soja" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Fondant au chocolat noir" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Mousse au chocolat" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Tiramisu" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Banana bread" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Cheesecake" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Croustade aux pommes" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Riz au lait" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Cookie au chocolat" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Semoule aux raisins" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +462,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -488,43 +487,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boeuf haché</t>
+          <t>Tomates</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>800</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Poivrons rouges</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Concombre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -535,75 +532,71 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ail</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Coriandre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gousse(s)</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Paprika</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Riz</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t xml:space="preserve">g </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Thym</t>
+          <t>Oignons rouges</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Saumon fumé</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>càs</t>
+          <t>tranche(s)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Oeufs</t>
+          <t>Citron vert</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -614,30 +607,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spaghetti</t>
+          <t xml:space="preserve">Avocat </t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Maïs</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>boîte</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sauce soja</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -688,12 +696,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz Arborio</t>
+          <t>Pâtes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -705,12 +713,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Champignons</t>
+          <t>Tomates cerises confites</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -722,12 +730,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Pesto vert</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -739,34 +747,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bouillon de légumes</t>
+          <t>Fromage râpé</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -817,12 +825,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pâtes</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -834,68 +842,66 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates cerises confites</t>
+          <t>Cumin</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pesto vert</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fromage râpé</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Coriandre</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>bouquet(s)</t>
         </is>
       </c>
     </row>
@@ -946,12 +952,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Haricots rouges</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -963,24 +969,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cumin</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -997,22 +1003,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coriandre</t>
+          <t>Épices Chili</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1022,7 +1030,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bouquet(s)</t>
+          <t>sachet(s)</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,7 +1056,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1073,13 +1081,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Haricots rouges</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+          <t>Riz à paella</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1090,34 +1096,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+          <t>Poivron rouge</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivron</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Petit pois (surgelés)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1131,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,17 +1143,77 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Chili</t>
+          <t>Gousse d'ail</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sachet(s)</t>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bouillon de volaille</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cube(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Safran ou Spigol</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>càc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>tranche(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Crevettes</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,7 +1239,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1202,11 +1264,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz à paella</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>400</v>
+          <t>Saucisses fumées</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1217,71 +1281,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivron rouge</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
+          <t>Tomates concassées</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Petit pois (surgelés)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>150</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Ail</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>gousse(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gousse d'ail</t>
+          <t>Curcuma</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Thym</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1289,52 +1357,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cube(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Safran ou Spigol</t>
+          <t>Riz Basmati</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>càc</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Chorizo</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>16</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>tranche(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Crevettes</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1385,7 +1423,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Saucisses fumées</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1402,24 +1440,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Pâte de curry rouge</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1429,48 +1467,48 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ail</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gousse(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Curcuma</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Thym</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1478,22 +1516,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>c.à.s</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Riz Basmati</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>250</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1549,46 +1572,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Poivron rouge</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pâte de curry rouge</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1623,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1612,32 +1635,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Gousse d'ail</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1688,29 +1711,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Lentilles vertes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivron rouge</t>
+          <t>Saucisses</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1722,12 +1745,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1744,7 +1767,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1756,32 +1779,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gousse d'ail</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cube(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Thym</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1832,12 +1855,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lentilles vertes</t>
+          <t>Viande hachée</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1849,12 +1872,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Saucisses</t>
+          <t>Feuilles de lasagne</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1866,66 +1889,94 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Sauce tomate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>60</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Gruyère râpé</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cube(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Thym</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1976,79 +2027,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+          <t>Cuisse de Lapin</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Feuilles de lasagne</t>
+          <t>Moutarde</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sauce tomate</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+          <t>Crème fraîche</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>25</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>60</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gruyère râpé</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+          <t>Tagliatelles</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2059,43 +2106,13 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Carottes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>50</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -2112,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,26 +2165,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tomates</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
+          <t>Semoule</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivrons rouges</t>
+          <t>Tomates</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2193,7 +2212,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coriandre</t>
+          <t>Persil</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2208,22 +2227,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>250</v>
+          <t>Menthe</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">g </t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oignons rouges</t>
+          <t>Oignons blancs ou rouges</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2238,45 +2259,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Saumon fumé</t>
+          <t>Citron</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tranche(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Citron vert</t>
+          <t>Huile Olive</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Avocat</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2327,11 +2333,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cuisse de Lapin</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2342,79 +2350,98 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Moutarde</t>
+          <t>Lardons</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>25</v>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tagliatelles</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>600</v>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carottes</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fromage rapé</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2465,29 +2492,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Filet mignon de porc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lardons</t>
+          <t>Champignons</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2499,79 +2526,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Échalote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Grenailles</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>c.à.s</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fromage rapé</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>100</v>
-      </c>
-      <c r="C9" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -2588,7 +2600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2624,12 +2636,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet mignon de porc</t>
+          <t>Viande hachée de bœuf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2641,12 +2653,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Champignons</t>
+          <t>Haricots rouges</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2658,29 +2670,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Échalote</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2692,30 +2704,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Épices Chili</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>sachet(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Grenailles</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Riz </t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>250</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -2768,12 +2795,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée de bœuf</t>
+          <t>Nouilles asiatiques</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2785,7 +2812,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Haricots rouges</t>
+          <t>Boeuf (rumsteack ou bavette)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2802,29 +2829,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Sauce soja</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2836,7 +2863,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Chili</t>
+          <t>Brocoli</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2846,18 +2873,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sachet(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2868,15 +2895,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riz </t>
+          <t>Coriandre</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>bouquet</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2902,7 +2929,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2927,12 +2954,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nouilles asiatiques</t>
+          <t>Encornets</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2944,46 +2971,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boeuf (rumsteack ou bavette)</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Pâte de curry vert</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2995,47 +3022,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brocoli</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Poivrons</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Coriandre</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>bouquet</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3098,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Encornets</t>
+          <t>Quinoa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3103,34 +3115,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Crevettes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pâte de curry vert</t>
+          <t>Bouillon de légumes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -3154,12 +3166,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3171,7 +3183,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Poivrons</t>
+          <t>Courgettes</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -3194,7 +3206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3230,12 +3242,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Quinoa</t>
+          <t>Pavé de saumon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3247,83 +3259,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crevettes</t>
+          <t>Poireaux</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bouillon de légumes</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Courgettes</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3374,12 +3371,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pavé de saumon</t>
+          <t>Crevettes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3391,68 +3388,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poireaux</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Citron vert</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Ail</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>gousse(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3503,7 +3515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Crevettes</t>
+          <t>Filets de poisson blanc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3520,63 +3532,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Pomme de terre</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>800</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Citron vert</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ail</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gousse(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Chapelure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3588,15 +3600,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carottes</t>
+          <t>Persil</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>botte</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ail</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gousse(s)</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3647,13 +3674,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filets de poisson blanc</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+          <t>Cabillaud</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3664,68 +3689,64 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pomme de terre</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+          <t>Tomates</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Echalotes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Citron</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chapelure</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>Ciboulette</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>bouquet</t>
         </is>
       </c>
     </row>
@@ -3747,15 +3768,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ail</t>
+          <t>Gingembre</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gousse(s)</t>
+          <t>racine</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Patates douces</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>700</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Crème fraîche</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3832,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3806,7 +3857,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Semoule</t>
+          <t>Lentilles corail</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3823,52 +3874,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
+          <t>Lait de coco</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concombre</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
+          <t>Tomates concassées</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Persil</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
+          <t>Curry</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Menthe</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3878,29 +3935,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oignons blancs ou rouges</t>
+          <t>Riz Basmati</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Citron</t>
+          <t>Coriandre ou basilic thaï</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -3908,7 +3965,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3959,37 +4016,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cabillaud</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>800</v>
+          <t>Pavé de saumon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>Sauce soja</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Echalotes</t>
+          <t>Miel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3999,99 +4060,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Citron</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ciboulette</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
+          <t>Brocoli</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bouquet</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Persil</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>botte</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Gingembre</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>racine</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Patates douces</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>700</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Crème fraîche</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4120,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Dessert</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -4142,63 +4145,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pavé de saumon</t>
+          <t>Chocolat noir</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Miel</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4210,17 +4213,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brocoli</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -4288,58 +4291,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Crème liquide</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4400,7 +4403,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chocolat noir</t>
+          <t>Biscuits à la cuillère</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4417,41 +4420,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Mascarpone</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème liquide</t>
+          <t>Café fort</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4468,12 +4471,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4493,7 +4496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4529,30 +4532,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Biscuits à la cuillère</t>
+          <t>Banane mûre</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mascarpone</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4563,34 +4564,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>85</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Café fort</t>
+          <t>Oeufs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4599,27 @@
           <t>Sucre</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="B7" t="n">
+        <v>160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Levure</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càc</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4658,28 +4670,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Banane mûre</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Biscuits speculoos</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>250</v>
+          <t>Fromage blanc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4690,43 +4702,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oeufs</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -4737,7 +4749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Levure</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4745,7 +4757,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>càc</t>
+          <t>càs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Oeufs</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Citron vert</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4796,47 +4838,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Biscuits speculoos</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>250</v>
+          <t>Pomme</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fromage blanc</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+          <t>Pâte Filo</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>feuille(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -4846,10 +4888,8 @@
           <t>Sucre</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="B6" t="n">
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -4860,60 +4900,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Armagnac ou Calvados</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>càs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Oeufs</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Citron vert</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>ml</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4964,47 +4959,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pomme</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Riz rond</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pâte Filo</t>
+          <t>Sucre vanillé</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feuille(s)</t>
+          <t>sachet</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beurre</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>50</v>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -5015,26 +5010,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Armagnac ou Calvados</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>50</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ml</t>
+          <t>càs</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5085,7 +5065,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz rond</t>
+          <t>Chocolat</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5100,32 +5080,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sucre vanillé</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sachet</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -5136,11 +5114,41 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>càs</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Levure</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càc</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5191,7 +5199,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chocolat</t>
+          <t>Semoule fine</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5206,26 +5214,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>l</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>150</v>
+          <t>Raisins secs</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5240,41 +5250,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Oeuf</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Levure</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>càc</t>
         </is>
       </c>
     </row>
@@ -5325,12 +5305,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lentilles corail</t>
+          <t>Lentilles vertes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5342,58 +5322,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Thym</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>càs</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Curry</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Bouillon de légumes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5403,128 +5383,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cube(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Riz Basmati</t>
+          <t>Persil</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Catégorie :</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Dessert</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ingrédient</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Quantité</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Unité</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Semoule fine</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Raisins secs</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sucre</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>g</t>
+          <t>botte(s)</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5550,7 +5424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -5575,85 +5449,105 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lentilles vertes</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
+          <t>Mangue verte (dure)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thym</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>càs</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carotte</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Coriandre ou basilic thaï</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Gingembre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>racine</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bouillon de légumes</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Cacahuètes</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cube(s)</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sauce soja</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Citron vert</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5679,7 +5573,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -5704,11 +5598,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mangue verte (dure)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+          <t>Courgette</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5719,11 +5615,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carottes</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>Aubergine</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5734,75 +5632,66 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coriandre</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
+          <t>Poivron</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gingembre</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>racine</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cacahuètes</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>50</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Herbes de Provence</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>càs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Citron vert</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5717,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -5853,30 +5742,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Courgette</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Pâtes fusili ou penne</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aubergine</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Tomates</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5887,29 +5772,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivron</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Feta</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Concombre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5921,7 +5804,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Basilic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5931,22 +5814,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Herbes de Provence</t>
+          <t>Olives noires</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>càs</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5972,7 +5855,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -5997,11 +5880,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pâtes fusili ou penne</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>400</v>
+          <t>Semoule</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -6012,7 +5897,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates</t>
+          <t>Poivrons</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6027,11 +5912,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Feta</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>80</v>
+          <t>Pois chiches</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -6042,24 +5929,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Concombre</t>
+          <t>Épices Ras el Hanout</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Basilic</t>
+          <t>Bouillon de légumes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6069,22 +5956,52 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>cube(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Olives noires</t>
+          <t>Courgettes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6135,7 +6052,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Semoule</t>
+          <t>Riz Arborio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6152,27 +6069,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivrons</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>Champignons</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pois chiches</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6184,24 +6103,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Épices Ras el Hanout</t>
+          <t>Bouillon de légumes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bouillon de légumes</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6210,51 +6129,6 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>cube(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Courgettes</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Carottes</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>

--- a/menu_actuel.xlsx
+++ b/menu_actuel.xlsx
@@ -7,45 +7,47 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Poke bowl au saumon" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Taboulé" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Dhal de lentilles" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lentilles vertes au thym" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Salade de mangue à la thaï" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Ratatouille" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Salade de pâtes tomates et feta" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Couscous aux légumes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Risotto forestier" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Gratin pâtes tomates &amp; pesto" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Galettes de carottes au cumin" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Chili sin carne" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Riz safrané au chorizo et crevettes" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Rougail saucisses" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Poulet au curry rouge" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Poulet basquaise" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Lentilles aux saucisses" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Lasagnes au boeuf" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Lapin à la moutarde" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Quiche lorraine" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Filet mignon sauce forestière" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Chili con carne" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Nouilles chinoises au boeuf" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Encornet au curry vert" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Risotto de quinoa aux crevettes" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Crumble poireaux saumon" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Crevettes au lait de coco" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Parmentier de poissons" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Cabillaud sauce vierge" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Saumon sauce soja" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Fondant au chocolat noir" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="Mousse au chocolat" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Tiramisu" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="Banana bread" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="Cheesecake" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="Croustade aux pommes" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="Riz au lait" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="Cookie au chocolat" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="Semoule aux raisins" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Tagliatelles carbonara" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Salade de pois chiches, tomates confites, feta" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Semoule aux raisins" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Taboulé" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dhal de lentilles corail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Poke bowl au saumon" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Lentilles vertes au thym" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Salade de mangue à la thaï" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Ratatouille" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Salade de pâtes tomates et feta" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Couscous aux légumes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Risotto forestier" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Gratin pâtes tomates &amp; pesto" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Galettes de carottes au cumin" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Chili sin carne" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Riz safrané au chorizo et crevettes" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Rougail saucisses" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Poulet au curry rouge" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Poulet basquaise" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Lentilles aux saucisses" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Lasagnes au boeuf" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Lapin à la moutarde" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Quiche lorraine" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Filet mignon sauce forestière" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Chili con carne" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Nouilles chinoises au boeuf" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Encornet au curry vert" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Risotto de quinoa aux crevettes" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Crumble poireaux saumon" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Crevettes au lait de coco" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Parmentier de poissons" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Cabillaud sauce vierge" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Saumon sauce soja" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Fondant au chocolat noir" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Mousse au chocolat" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Tiramisu" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Banana bread" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Cheesecake" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Croustade aux pommes" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Riz au lait" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Cookie au chocolat" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,7 +464,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -487,165 +489,94 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tomates</t>
+          <t>Lardons</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivrons rouges</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
+          <t xml:space="preserve">Tagliatelles </t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concombre</t>
+          <t>Crème fraiche</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coriandre</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Fromage rapé</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">g </t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oignons rouges</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Saumon fumé</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>tranche(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Citron vert</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avocat </t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Maïs</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>boîte</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sauce soja</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>10</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>cl</t>
         </is>
       </c>
     </row>
@@ -660,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,7 +602,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -696,13 +627,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pâtes</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+          <t>Pâtes fusili ou penne</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -713,30 +642,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates cerises confites</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+          <t>Tomates</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pesto vert</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+          <t>Feta</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -747,34 +672,49 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fromage râpé</t>
+          <t>Concombre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Basilic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>botte</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Olives noires</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -789,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -825,12 +765,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Semoule</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -842,45 +782,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cumin</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Poivrons</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Pois chiches</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
+          <t>Épices Ras el Hanout</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -891,7 +831,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coriandre</t>
+          <t>Bouillon de légumes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -901,7 +841,52 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bouquet(s)</t>
+          <t>cube(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Courgettes</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -952,12 +937,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Haricots rouges</t>
+          <t>Riz Arborio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -969,12 +954,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Champignons</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -986,24 +971,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Bouillon de légumes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1013,14 +998,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Chili</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1030,7 +1015,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sachet(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,7 +1041,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1081,11 +1066,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz à paella</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>400</v>
+          <t>Pâtes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1096,26 +1083,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivron rouge</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
+          <t>Tomates cerises confites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Petit pois (surgelés)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>150</v>
+          <t>Pesto vert</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1126,94 +1117,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Fromage râpé</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gousse d'ail</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Bouillon de volaille</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>cube(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Safran ou Spigol</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>càc</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Chorizo</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>16</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>tranche(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Crevettes</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1239,7 +1170,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1264,7 +1195,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Saucisses fumées</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1281,24 +1212,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Cumin</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1315,24 +1246,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ail</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gousse(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Curcuma</t>
+          <t>Coriandre</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1342,37 +1271,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>c.à.s</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Thym</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>c.à.s</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Riz Basmati</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>250</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>g</t>
+          <t>bouquet(s)</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1398,7 +1297,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1423,12 +1322,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Haricots rouges</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1440,24 +1339,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pâte de curry rouge</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1467,7 +1366,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1491,32 +1390,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Épices Chili</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Poivron</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>sachet(s)</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1542,7 +1426,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1567,17 +1451,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Riz à paella</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1587,10 +1469,8 @@
           <t>Poivron rouge</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1601,17 +1481,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomate</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Petit pois (surgelés)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1652,15 +1530,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cube(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Safran ou Spigol</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>càc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>tranche(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Crevettes</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1711,12 +1634,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lentilles vertes</t>
+          <t>Saucisses fumées</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1728,24 +1651,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Saucisses</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1762,24 +1685,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Ail</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>gousse(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Curcuma</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1789,7 +1712,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cube(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
@@ -1805,6 +1728,21 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>c.à.s</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Riz Basmati</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>250</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,7 +1793,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1872,61 +1810,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Feuilles de lasagne</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sauce tomate</t>
+          <t>Pâte de curry rouge</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>60</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gruyère râpé</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1938,43 +1878,13 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>50</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -2027,11 +1937,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cuisse de Lapin</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
+          <t>Filet de poulet</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2042,7 +1954,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Moutarde</t>
+          <t>Poivron rouge</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2052,22 +1964,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>25</v>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -2091,30 +2005,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tagliatelles</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>600</v>
+          <t>Gousse d'ail</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carottes</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,13 +2081,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Semoule</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+          <t>Pois chiches</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2182,37 +2096,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates</t>
+          <t>Tomates confites</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concombre</t>
+          <t>Feta</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Persil</t>
+          <t>Menthe</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2220,31 +2134,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>bouquet</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Menthe</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Oignons rouges</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oignons blancs ou rouges</t>
+          <t>Concombre</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2263,26 +2175,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Huile Olive</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>10</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>cl</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2333,46 +2230,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Lentilles vertes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lardons</t>
+          <t>Saucisses</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2384,41 +2281,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>cube(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Thym</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2427,21 +2324,6 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>c.à.s</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fromage rapé</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>100</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>g</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2492,12 +2374,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet mignon de porc</t>
+          <t>Viande hachée</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2509,63 +2391,61 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Champignons</t>
+          <t>Feuilles de lasagne</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Sauce tomate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Échalote</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>60</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Gruyère râpé</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2577,15 +2457,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Grenailles</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2636,51 +2546,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée de bœuf</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+          <t>Cuisse de Lapin</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Haricots rouges</t>
+          <t>Moutarde</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+          <t>Crème fraîche</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>25</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2598,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2704,47 +2610,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Chili</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Tagliatelles</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sachet(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Carottes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Riz </t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>250</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>g</t>
         </is>
       </c>
     </row>
@@ -2795,29 +2684,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nouilles asiatiques</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boeuf (rumsteack ou bavette)</t>
+          <t>Lardons</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2829,81 +2718,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brocoli</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Coriandre</t>
+          <t>Fromage rapé</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bouquet</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2818,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2954,7 +2843,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Encornets</t>
+          <t>Filet mignon de porc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2971,46 +2860,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Champignons</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pâte de curry vert</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Échalote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3022,12 +2911,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3039,15 +2928,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Poivrons</t>
+          <t>Grenailles</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -3062,7 +2951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3073,7 +2962,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3098,12 +2987,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Quinoa</t>
+          <t>Viande hachée de bœuf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3115,7 +3004,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crevettes</t>
+          <t>Haricots rouges</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3132,17 +3021,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bouillon de légumes</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -3166,24 +3055,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Épices Chili</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>sachet(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Courgettes</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -3192,6 +3081,21 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Riz </t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>250</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3217,7 +3121,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3242,12 +3146,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pavé de saumon</t>
+          <t>Nouilles asiatiques</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3259,68 +3163,98 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poireaux</t>
+          <t>Boeuf (rumsteack ou bavette)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Sauce soja</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Brocoli</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Coriandre</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bouquet</t>
         </is>
       </c>
     </row>
@@ -3371,12 +3305,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Crevettes</t>
+          <t>Encornets</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3405,34 +3339,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Citron vert</t>
+          <t>Pâte de curry vert</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ail</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gousse(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -3456,11 +3390,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carottes</t>
+          <t>Poivrons</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3479,7 +3413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,12 +3449,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filets de poisson blanc</t>
+          <t>Quinoa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3532,12 +3466,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pomme de terre</t>
+          <t>Crevettes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3549,46 +3483,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Bouillon de légumes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chapelure</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3600,30 +3534,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Persil</t>
+          <t>Courgettes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>botte</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ail</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>gousse(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3674,11 +3593,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cabillaud</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>800</v>
+          <t>Pavé de saumon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3689,11 +3610,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>Poireaux</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3704,109 +3627,66 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Echalotes</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Citron</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ciboulette</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
+          <t>Crème fraîche</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bouquet</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Persil</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>botte</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Gingembre</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>racine</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Patates douces</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>700</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Crème fraîche</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3832,7 +3712,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Dessert</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3857,13 +3737,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lentilles corail</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+          <t>Semoule fine</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3874,29 +3752,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>l</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Raisins secs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3908,64 +3784,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Curry</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c.à.s</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Riz Basmati</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>250</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Coriandre ou basilic thaï</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>botte</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4016,29 +3843,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pavé de saumon</t>
+          <t>Crevettes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4050,49 +3877,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Miel</t>
+          <t>Citron vert</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Ail</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>gousse(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brocoli</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -4109,7 +3951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4120,7 +3962,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Dessert</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -4145,12 +3987,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chocolat noir</t>
+          <t>Filets de poisson blanc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4162,12 +4004,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Pomme de terre</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>800</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4179,29 +4021,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4213,17 +4055,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Chapelure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Persil</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>botte</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ail</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gousse(s)</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4249,7 +4121,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Dessert</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -4274,13 +4146,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chocolat noir</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+          <t>Cabillaud</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4291,13 +4161,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oeuf</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Tomates</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4308,51 +4176,109 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Echalotes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème liquide</t>
+          <t>Citron</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beurre</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>Ciboulette</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>bouquet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Persil</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>botte</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gingembre</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>racine</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Patates douces</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>700</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Crème fraîche</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4304,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Dessert</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -4403,85 +4329,85 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Biscuits à la cuillère</t>
+          <t>Pavé de saumon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mascarpone</t>
+          <t>Sauce soja</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Miel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Café fort</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Brocoli</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4532,28 +4458,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Banane mûre</t>
+          <t>Chocolat noir</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>250</v>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4564,62 +4492,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beurre</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>85</v>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oeufs</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sucre</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>160</v>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Levure</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>càc</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4670,11 +4587,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Biscuits speculoos</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>250</v>
+          <t>Chocolat noir</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4685,49 +4604,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fromage blanc</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>25</v>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Crème liquide</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -4737,57 +4658,14 @@
           <t>Beurre</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>125</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>càs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Oeufs</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Citron vert</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -4838,77 +4716,85 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pomme</t>
+          <t>Biscuits à la cuillère</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pâte Filo</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>12</v>
+          <t>Mascarpone</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feuille(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beurre</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>50</v>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sucre</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>50</v>
+          <t>Café fort</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Armagnac ou Calvados</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>50</v>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4959,62 +4845,94 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz rond</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>100</v>
+          <t>Banane mûre</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sucre vanillé</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sachet</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>85</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Oeufs</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Sucre</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>càs</t>
+      <c r="B7" t="n">
+        <v>160</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Levure</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càc</t>
         </is>
       </c>
     </row>
@@ -5029,7 +4947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5065,11 +4983,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chocolat</t>
+          <t>Biscuits speculoos</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5080,11 +4998,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Beurre</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>85</v>
+          <t>Fromage blanc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5095,15 +5015,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -5113,8 +5033,10 @@
           <t>Sucre</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>85</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5125,30 +5047,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Levure</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Oeufs</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Citron vert</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>càc</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5199,43 +5151,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Semoule fine</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>100</v>
+          <t>Pomme</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Pâte Filo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>feuille(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Raisins secs</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5250,11 +5202,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Armagnac ou Calvados</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ml</t>
         </is>
       </c>
     </row>
@@ -5269,6 +5236,280 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Entrée</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Semoule</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tomates</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Concombre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Persil</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>botte</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Menthe</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>botte</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Oignons blancs ou rouges</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Citron</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Huile Olive</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cl</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Riz rond</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sucre vanillé</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sachet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>càs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -5280,7 +5521,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Dessert</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -5305,13 +5546,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lentilles vertes</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
+          <t>Chocolat</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5322,75 +5561,67 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thym</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>85</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>càs</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carotte</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>85</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bouillon de légumes</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cube(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Persil</t>
+          <t>Levure</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5398,7 +5629,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>botte(s)</t>
+          <t>càc</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5655,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -5449,97 +5680,107 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mangue verte (dure)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+          <t>Lentilles corail</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carottes</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>Lait de coco</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coriandre ou basilic thaï</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
+          <t>Tomates concassées</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gingembre</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
+          <t>Curry</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>racine</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cacahuètes</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>50</v>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Riz Basmati</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>càs</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Citron vert</t>
+          <t>Coriandre ou basilic thaï</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5547,7 +5788,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5573,7 +5814,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -5598,13 +5839,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Courgette</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Tomates</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5615,13 +5854,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aubergine</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Poivrons rouges</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5632,13 +5869,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivron</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Concombre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5649,41 +5884,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tomate</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Coriandre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Riz</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t xml:space="preserve">g </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Herbes de Provence</t>
+          <t>Oignons rouges</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5691,7 +5922,82 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>càs</t>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Saumon fumé</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>tranche(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Citron vert</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avocat </t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Maïs</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>boîte</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sauce soja</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -5717,7 +6023,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -5742,11 +6048,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pâtes fusili ou penne</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>400</v>
+          <t>Lentilles vertes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5757,37 +6065,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>Thym</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>càs</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Feta</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>80</v>
+          <t>Carotte</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Concombre</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5804,7 +6116,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Basilic</t>
+          <t>Bouillon de légumes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5814,22 +6126,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>cube(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Olives noires</t>
+          <t>Persil</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>botte(s)</t>
         </is>
       </c>
     </row>
@@ -5844,7 +6156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5855,7 +6167,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -5880,24 +6192,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Semoule</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+          <t>Mangue verte (dure)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivrons</t>
+          <t>Carottes</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5912,94 +6222,73 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pois chiches</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+          <t>Coriandre ou basilic thaï</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Épices Ras el Hanout</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Gingembre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>racine</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bouillon de légumes</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Cacahuètes</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cube(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Courgettes</t>
+          <t>Sauce soja</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>càs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Citron vert</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Carottes</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -6016,7 +6305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6052,68 +6341,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz Arborio</t>
+          <t>Courgette</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Champignons</t>
+          <t>Aubergine</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bouillon de légumes</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -6131,6 +6420,21 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Herbes de Provence</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càs</t>
         </is>
       </c>
     </row>

--- a/menu_actuel.xlsx
+++ b/menu_actuel.xlsx
@@ -7,33 +7,39 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pancakes épinards saumon" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Blanquette de Veau" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Clafoutis jambon courgettes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Risotto aux Crevettes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Quiche Au Thon" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tortilla quiche au jambon" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Crumble salé au poulet" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Poulet Basquaise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Poulet miel soja " sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Lasagnes Bolognaise" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Risotto aux Champignons" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Hachis Parmentier" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Chili con Carne" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Curry de Pois Chiches" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Tartiflette" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Quiche Lorraine" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Poulet Coco Curry" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Ratatouille" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Pâtes Carbonara" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Saumon Teriyaki" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Wok Nouilles Crevettes" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Salade César" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Tajine Poulet Citron" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Paella Express" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Gnocchis Pesto Tomates" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Mousse au Chocolat" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Mi-Cuit Chocolat" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Poke bowl au saumon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Salade de pois chiches- tomates confites-feta " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Croustade aux pommes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Riz au lait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cookies au chocolat" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Crumble pommes fraises" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Pancakes épinards saumon" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Blanquette de Veau" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Clafoutis jambon courgettes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Risotto aux Crevettes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Quiche Au Thon" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Tortilla quiche au jambon" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Crumble salé au poulet" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Poulet Basquaise" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Poulet miel soja " sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Lasagnes Bolognaise" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Risotto aux Champignons" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Hachis Parmentier" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Chili con Carne" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Curry de Pois Chiches" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Tartiflette" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Quiche Lorraine" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Poulet Coco Curry" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Ratatouille" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Pâtes Carbonara" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Saumon Teriyaki" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Wok Nouilles Crevettes" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Salade César" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Tajine Poulet Citron" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Paella Express" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Gnocchis Pesto Tomates" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Mousse au Chocolat" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Mi-Cuit Chocolat" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,7 +456,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -475,26 +481,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Tomates</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oeufs</t>
+          <t>Poivrons rouges</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -505,60 +511,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Concombre</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Epinards frais</t>
+          <t>Coriandre</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Levure</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>càc</t>
+          <t xml:space="preserve">g </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Oignons rouges</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -569,41 +575,71 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>tranche(s)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fromage blanc</t>
+          <t>Citron vert</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ciboulette</t>
+          <t xml:space="preserve">Avocat </t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Maïs</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>botte</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>boîte</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sauce soja</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -618,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,7 +665,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -654,11 +690,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
+          <t>Riz Arborio</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -669,26 +705,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Feuilles de lasagne</t>
+          <t>Crevettes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sauce tomate</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -699,58 +735,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gruyère râpé</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Petits pois</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>100</v>
-      </c>
-      <c r="C9" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -767,7 +788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,7 +799,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -803,26 +824,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz Arborio</t>
+          <t>Pâte brisée</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Champignons</t>
+          <t>Thon</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -833,45 +854,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fromage rapé</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>200</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -886,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,7 +933,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -922,75 +958,105 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
+          <t>Tortilla de blé</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>grande(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pomme de terre</t>
+          <t>Oeufs</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>800</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Jambon</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t xml:space="preserve">g </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Emmental</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ml</t>
         </is>
       </c>
     </row>
@@ -1041,11 +1107,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1056,75 +1122,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Haricots rouges</t>
+          <t>Aubergine</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>400</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Chili</t>
+          <t>Chapelure</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sachet(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1150,7 +1216,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1175,52 +1241,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pois chiches (conserve)</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Poivron rouge</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>400</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pâte de curry</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1228,52 +1294,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Gousse d'ail</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Coriandre</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>bouquet</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1324,75 +1375,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pomme de terre</t>
+          <t>Filet de Poulet</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reblochon</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lardons</t>
+          <t>Poivrons</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Miel</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Soja</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>ml</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1418,7 +1469,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1443,56 +1494,56 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pâte brisée</t>
+          <t>Viande hachée</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lardons</t>
+          <t>Feuilles de lasagne</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200</v>
+        <v>12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Sauce tomate</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1503,28 +1554,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Gruyère râpé</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Emmental</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -1552,7 +1618,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1577,52 +1643,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Riz Arborio</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Champignons</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poudre de curry</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1630,22 +1696,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1737,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1696,60 +1762,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Courgette</t>
+          <t>Viande hachée</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aubergine</t>
+          <t>Pomme de terre</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1815,11 +1881,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spaghetti</t>
+          <t>Viande hachée</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1830,11 +1896,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lardons</t>
+          <t>Haricots rouges</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1845,43 +1911,58 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pecorino ou Parmesan</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Épices Chili</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>sachet(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Poivron</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -1909,7 +1990,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1934,11 +2015,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande de veau</t>
+          <t>Pois chiches</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1949,26 +2030,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Tomates confites</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Champignon de Paris</t>
+          <t>Feta</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1979,22 +2060,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Menthe</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>bouquet</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Oignons rouges</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2002,33 +2083,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cube(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Concombre</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Poireau</t>
+          <t>Citron</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2047,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2058,7 +2139,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2083,26 +2164,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pavé de saumon</t>
+          <t>Pois chiches (conserve)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2113,45 +2194,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Miel</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Pâte de curry</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brocoli</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>250</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Coriandre</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bouquet</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2288,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2202,75 +2313,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nouilles asiatiques</t>
+          <t>Pomme de terre</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crevettes décortiquées</t>
+          <t>Reblochon</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Lardons</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brocoli</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2321,7 +2432,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Salade Romaine</t>
+          <t>Pâte brisée</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2336,105 +2447,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Lardons</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Croûtons</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sauce César</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pot</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Emmental</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Tomate</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Concombre</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2485,7 +2566,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cuisse de poulet</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2500,30 +2581,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Citron confit</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Olives vertes</t>
+          <t>Poudre de curry</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2615,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2545,60 +2626,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Tajine</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>c.à.s</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Couscous</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>500</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Courgette</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Poivron</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2624,7 +2660,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2649,103 +2685,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz à paella</t>
+          <t>Courgette</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crevettes</t>
+          <t>Aubergine</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Petit pois</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Safran ou Spigol</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cube ou bouillon</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -2762,7 +2768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,7 +2779,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2798,11 +2804,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gnocchis</t>
+          <t>Spaghetti</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2813,11 +2819,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pesto vert</t>
+          <t xml:space="preserve"> Lardons</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2828,30 +2834,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates confites</t>
+          <t>Crème</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Pecorino ou Parmesan</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2898,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Dessert</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2902,75 +2923,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chocolat noir</t>
+          <t>Pavé de saumon</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Sauce soja</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Miel</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème liquide</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Brocoli</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3017,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Dessert</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3021,11 +3042,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chocolat noir</t>
+          <t>Nouilles asiatiques</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3036,11 +3057,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Crevettes décortiquées</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3051,11 +3072,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3066,30 +3087,358 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Sauce soja</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Brocoli</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Entrée</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Salade Romaine</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Filet de poulet</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Croûtons</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Parmesan</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sauce César</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>pot</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Concombre</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Plat viande</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cuisse de poulet</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Citron confit</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Olives vertes</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Épices Tajine</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>c.à.s</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Couscous</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Courgette</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Poivron</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -3104,6 +3453,112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Pomme</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Pâte Filo</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>feuille(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3115,7 +3570,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3140,22 +3595,171 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Courgettes</t>
+          <t>Riz à paella</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jambon</t>
+          <t>Crevettes</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>200</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Petit pois</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Safran ou Spigol</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cube ou bouillon</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Plat végé</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gnocchis</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>600</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Pesto vert</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -3170,11 +3774,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Feta</t>
+          <t>Tomates confites</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3185,58 +3789,251 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oeufs</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chocolat noir</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>200</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Crème liquide</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Emmental</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>50</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chocolat noir</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>150</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Farine</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>60</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -3253,7 +4050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3264,7 +4061,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Dessert</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3289,11 +4086,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz Arborio</t>
+          <t>Riz rond</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3304,75 +4101,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crevettes</t>
+          <t>Sucre vanillé</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>sachet</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Parmesan</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>80</v>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Oignon</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Petits pois</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>100</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>g</t>
+          <t>càs</t>
         </is>
       </c>
     </row>
@@ -3398,7 +4167,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Dessert</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3423,26 +4192,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pâte brisée</t>
+          <t>Chocolat</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thon</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3453,60 +4222,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fromage rapé</t>
+          <t>Levure</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>càc</t>
         </is>
       </c>
     </row>
@@ -3521,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3532,7 +4301,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Dessert</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3557,105 +4326,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tortilla de blé</t>
+          <t>Pommes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>grande(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oeufs</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jambon</t>
+          <t>Fraises</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">g </t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Emmental</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>100</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">g </t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>100</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -3670,7 +4409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3681,7 +4420,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3706,11 +4445,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3721,11 +4460,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aubergine</t>
+          <t>Oeufs</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3736,26 +4475,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>ml</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Epinards frais</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3766,15 +4505,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chapelure</t>
+          <t>Levure</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>càc</t>
         </is>
       </c>
     </row>
@@ -3790,6 +4529,51 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Saumon fumé</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>200</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fromage blanc</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>150</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ciboulette</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>botte</t>
         </is>
       </c>
     </row>
@@ -3804,7 +4588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3840,26 +4624,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Viande de veau</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivron rouge</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3870,45 +4654,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Champignon de Paris</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gousse d'ail</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cube(s)</t>
         </is>
       </c>
     </row>
@@ -3924,6 +4708,21 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Poireau</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -3938,7 +4737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3949,7 +4748,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3974,26 +4773,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de Poulet</t>
+          <t>Courgettes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Jambon</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4004,45 +4803,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivrons</t>
+          <t>Feta</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Miel</t>
+          <t>Oeufs</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Soja</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>200</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Emmental</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>60</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ml</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>

--- a/menu_actuel.xlsx
+++ b/menu_actuel.xlsx
@@ -7,39 +7,40 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Poke bowl au saumon" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Salade de pois chiches- tomates confites-feta " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Croustade aux pommes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Riz au lait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cookies au chocolat" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Crumble pommes fraises" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Pancakes épinards saumon" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Blanquette de Veau" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Clafoutis jambon courgettes" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Risotto aux Crevettes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Quiche Au Thon" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Tortilla quiche au jambon" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Crumble salé au poulet" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Poulet Basquaise" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Poulet miel soja " sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Lasagnes Bolognaise" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Risotto aux Champignons" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Hachis Parmentier" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Chili con Carne" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Curry de Pois Chiches" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Tartiflette" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Quiche Lorraine" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Poulet Coco Curry" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Ratatouille" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Pâtes Carbonara" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Saumon Teriyaki" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Wok Nouilles Crevettes" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Salade César" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Tajine Poulet Citron" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Paella Express" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Gnocchis Pesto Tomates" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="Mousse au Chocolat" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Mi-Cuit Chocolat" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Dahl de lentilles corail aux crevettes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Poke bowl au saumon" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Salade de pois chiches- tomates confites-feta " sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Croustade aux pommes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Riz au lait" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cookies au chocolat" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Crumble pommes fraises" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Pancakes épinards saumon" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Blanquette de Veau" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Clafoutis jambon courgettes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Risotto aux Crevettes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Quiche Au Thon" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Tortilla quiche au jambon" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Crumble salé au poulet" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Poulet Basquaise" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Poulet miel soja " sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Lasagnes Bolognaise" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Risotto aux Champignons" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Hachis Parmentier" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Chili con Carne" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Curry de Pois Chiches" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Tartiflette" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Quiche Lorraine" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Poulet Coco Curry" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Ratatouille" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Pâtes Carbonara" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Saumon Teriyaki" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Wok Nouilles Crevettes" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Salade César" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Tajine Poulet Citron" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Paella Express" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Gnocchis Pesto Tomates" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Mousse au Chocolat" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Mi-Cuit Chocolat" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +457,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -481,37 +482,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tomates</t>
+          <t>Lentilles corail</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivrons rouges</t>
+          <t>Crevettes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concombre</t>
+          <t>Coriandre</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -519,14 +520,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>bouquet</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coriandre</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -534,112 +535,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>botte</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">g </t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oignons rouges</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Saumon fumé</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>tranche(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Citron vert</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avocat </t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Maïs</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>boîte</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sauce soja</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>10</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>cl</t>
         </is>
       </c>
     </row>
@@ -654,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,7 +591,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -690,26 +616,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz Arborio</t>
+          <t>Courgettes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crevettes</t>
+          <t>Jambon</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -720,11 +646,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Feta</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -735,43 +661,58 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Oeufs</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>ml</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Petits pois</t>
+          <t>Emmental</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>60</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -799,7 +740,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -824,26 +765,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pâte brisée</t>
+          <t>Riz Arborio</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thon</t>
+          <t>Crevettes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -854,56 +795,56 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fromage rapé</t>
+          <t>Petits pois</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -922,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,105 +899,90 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tortilla de blé</t>
+          <t>Pâte brisée</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>grande(s)</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oeufs</t>
+          <t>Thon</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jambon</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">g </t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Emmental</t>
+          <t>Fromage rapé</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">g </t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>100</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1071,7 +997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,7 +1008,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1107,26 +1033,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Tortilla de blé</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>grande(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aubergine</t>
+          <t>Oeufs</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1137,60 +1063,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Jambon</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t xml:space="preserve">g </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chapelure</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Emmental</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
+          <t xml:space="preserve">g </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ml</t>
         </is>
       </c>
     </row>
@@ -1245,22 +1186,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Poivron rouge</t>
+          <t>Aubergine</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1286,41 +1227,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gousse d'ail</t>
+          <t>Chapelure</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1375,41 +1316,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de Poulet</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>600</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Poivron rouge</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>220</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivrons</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1420,30 +1361,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Miel</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Soja</t>
+          <t>Gousse d'ail</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Riz</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>240</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,11 +1450,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
+          <t>Filet de Poulet</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1509,90 +1465,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Feuilles de lasagne</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sauce tomate</t>
+          <t>Poivrons</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Miel</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gruyère râpé</t>
+          <t>Soja</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Beurre</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>100</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>100</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1618,7 +1544,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1643,11 +1569,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz Arborio</t>
+          <t>Viande hachée</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1658,26 +1584,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Champignons</t>
+          <t>Feuilles de lasagne</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>300</v>
+        <v>12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Sauce tomate</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1688,30 +1614,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Gruyère râpé</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1693,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1762,11 +1718,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande hachée</t>
+          <t>Riz Arborio</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1777,11 +1733,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pomme de terre</t>
+          <t>Champignons</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1792,30 +1748,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1782,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1845,7 +1801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1896,11 +1852,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Haricots rouges</t>
+          <t>Pomme de terre</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1911,58 +1867,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Chili</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>sachet(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Poivron</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -1979,7 +1920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2015,52 +1956,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pois chiches</t>
+          <t>Tomates</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tomates confites</t>
+          <t>Poivrons rouges</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Feta</t>
+          <t>Concombre</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Menthe</t>
+          <t>Coriandre</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2068,29 +2009,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bouquet</t>
+          <t>botte</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignons rouges</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t xml:space="preserve">g </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Concombre</t>
+          <t>Oignons rouges</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2105,15 +2046,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Citron</t>
+          <t>Saumon fumé</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>tranche(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Citron vert</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avocat </t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Maïs</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>boîte</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sauce soja</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,7 +2140,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2164,11 +2165,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pois chiches (conserve)</t>
+          <t>Viande hachée</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2179,15 +2180,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Haricots rouges</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -2209,37 +2210,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pâte de curry</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Épices Chili</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>sachet(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2248,21 +2249,6 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Coriandre</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>bouquet</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2288,7 +2274,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2313,41 +2299,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pomme de terre</t>
+          <t>Pois chiches (conserve)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reblochon</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lardons</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2358,7 +2344,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Pâte de curry</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2366,22 +2352,52 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Coriandre</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bouquet</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2407,7 +2423,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2432,7 +2448,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pâte brisée</t>
+          <t>Pomme de terre</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2440,82 +2456,67 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lardons</t>
+          <t>Reblochon</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Lardons</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>cl</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Emmental</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>150</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>g</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2541,7 +2542,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2566,11 +2567,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Pâte brisée</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2581,58 +2582,73 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Lardons</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poudre de curry</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Emmental</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>150</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -2660,7 +2676,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2685,11 +2701,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Courgette</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2700,22 +2716,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aubergine</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Poudre de curry</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2723,18 +2739,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2745,15 +2761,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2795,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2804,60 +2820,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spaghetti</t>
+          <t>Courgette</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lardons</t>
+          <t>Aubergine</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crème</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pecorino ou Parmesan</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2914,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -2923,56 +2939,56 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pavé de saumon</t>
+          <t>Spaghetti</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t xml:space="preserve"> Lardons</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Miel</t>
+          <t>Crème</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Riz basmati</t>
+          <t>Pecorino ou Parmesan</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2983,7 +2999,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brocoli</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -3042,37 +3058,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nouilles asiatiques</t>
+          <t>Pavé de saumon</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crevettes décortiquées</t>
+          <t>Sauce soja</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Miel</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3080,22 +3096,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sauce soja</t>
+          <t>Riz basmati</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3136,7 +3152,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3161,118 +3177,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Salade Romaine</t>
+          <t>Nouilles asiatiques</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Filet de poulet</t>
+          <t>Crevettes décortiquées</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Croûtons</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Sauce soja</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sauce César</t>
+          <t>Brocoli</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>pot</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Oeuf</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Tomate</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Concombre</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -3300,7 +3271,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3325,11 +3296,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cuisse de poulet</t>
+          <t>Salade Romaine</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3340,7 +3311,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Citron confit</t>
+          <t>Filet de poulet</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -3355,7 +3326,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Olives vertes</t>
+          <t>Croûtons</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3370,22 +3341,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Épices Tajine</t>
+          <t>Sauce César</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -3393,29 +3364,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>c.à.s</t>
+          <t>pot</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Couscous</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Courgette</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -3430,7 +3401,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Concombre</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -3453,7 +3424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3464,7 +3435,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Dessert</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3489,43 +3460,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pomme</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Pois chiches</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pâte Filo</t>
+          <t>Tomates confites</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feuille(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Feta</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3536,15 +3505,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Menthe</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>bouquet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Oignons rouges</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Concombre</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Citron</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3570,7 +3584,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3595,37 +3609,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz à paella</t>
+          <t>Cuisse de poulet</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crevettes</t>
+          <t>Citron confit</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Olives vertes</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3640,22 +3654,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Petit pois</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Safran ou Spigol</t>
+          <t>Épices Tajine</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -3663,35 +3677,50 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dose</t>
+          <t>c.à.s</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cube ou bouillon</t>
+          <t>Couscous</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Courgette</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Poivron</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>pièce(s)</t>
         </is>
@@ -3708,7 +3737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3719,7 +3748,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat végé</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3744,11 +3773,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gnocchis</t>
+          <t>Riz à paella</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3759,11 +3788,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pesto vert</t>
+          <t>Crevettes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3774,11 +3803,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomates confites</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3789,15 +3818,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Petit pois</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Safran ou Spigol</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cube ou bouillon</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3823,7 +3897,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Dessert</t>
+          <t>Plat végé</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -3848,11 +3922,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chocolat noir</t>
+          <t>Gnocchis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3863,26 +3937,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oeuf</t>
+          <t>Pesto vert</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Tomates confites</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3893,28 +3967,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème liquide</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t>cl</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Beurre</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>30</v>
-      </c>
-      <c r="C7" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -3971,6 +4030,125 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>200</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Oeuf</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Crème liquide</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catégorie :</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chocolat noir</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>150</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -4086,47 +4264,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riz rond</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>100</v>
+          <t>Pomme</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sucre vanillé</t>
+          <t>Pâte Filo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sachet</t>
+          <t>feuille(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -4137,11 +4315,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>càs</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4192,7 +4370,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chocolat</t>
+          <t>Riz rond</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4207,30 +4385,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Sucre vanillé</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>sachet</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>150</v>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
@@ -4241,41 +4421,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Oeuf</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>pièce(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Levure</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>càc</t>
+          <t>càs</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4326,26 +4476,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pommes</t>
+          <t>Chocolat</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4356,11 +4506,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fraises</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4371,11 +4521,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -4386,15 +4536,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Oeuf</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Levure</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>càc</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4420,7 +4585,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat poisson</t>
+          <t>Dessert</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -4445,56 +4610,56 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Pommes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oeufs</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Fraises</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Epinards frais</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -4505,75 +4670,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Levure</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>càc</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Parmesan</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>50</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Saumon fumé</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>200</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fromage blanc</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>150</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Ciboulette</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>botte</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4599,7 +4704,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat viande</t>
+          <t>Plat poisson</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -4624,11 +4729,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viande de veau</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>800</v>
+        <v>150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4639,11 +4744,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carotte</t>
+          <t>Oeufs</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4654,37 +4759,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Champignon de Paris</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crème fraîche</t>
+          <t>Epinards frais</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cl</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bouillon de volaille</t>
+          <t>Levure</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4692,18 +4797,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cube(s)</t>
+          <t>càc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -4714,15 +4819,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Poireau</t>
+          <t>Saumon fumé</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fromage blanc</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>150</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ciboulette</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>botte</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4883,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Plat viande</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -4773,41 +4908,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Courgettes</t>
+          <t>Viande de veau</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jambon</t>
+          <t>Carotte</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Feta</t>
+          <t>Champignon de Paris</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4818,41 +4953,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oeufs</t>
+          <t>Crème fraîche</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pièce(s)</t>
+          <t>cl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Bouillon de volaille</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>cube(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Emmental</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -4863,15 +4998,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Poireau</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pièce(s)</t>
         </is>
       </c>
     </row>
